--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -777,43 +777,43 @@
   <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.22265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="17.33984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.33984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="10.04296875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="138.23828125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="118.515625" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="68.94921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="59.11328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationquantity.xlsx
@@ -266,8 +266,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
   </si>
   <si>
     <t>SN (see also Range) or CQ</t>
@@ -286,10 +286,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -309,13 +309,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -331,8 +331,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Quantity.value</t>
@@ -354,10 +354,10 @@
     <t>暗示された精度については常に尊重すべきである。貨幣計算では制度に関する独自のルールがある（会計についての標準的な教科書を参照すること）。</t>
   </si>
   <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>精度は、測定のほとんどすべての場合に暗黙的に処理されます。 / Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -386,7 +386,7 @@
     <t>計測法に制限があって値が&lt;5ug/L や &gt;400mg/L として示されるような場合でも値を扱えるようなフレームワークが必要である。</t>
   </si>
   <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
+    <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
     <t>required</t>
@@ -461,7 +461,7 @@
     <t>単位のコード化された形式、【JP Core仕様】MERIT9医薬品単位略号マスタコードを推奨(**SHOULD**)されるが、ローカルコード等を利用することも可能とする</t>
   </si>
   <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+    <t>すべてのフォームに固定されたユニットの計算可能な形式が必要です。UCUMはこれを数量で提供しますが、Snomed CTは多くの関心のある単位を提供します。 / Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
   </si>
   <si>
     <t>preferred</t>
@@ -791,7 +791,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="118.515625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="194.171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
